--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\bupt_icpc_rankings\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F3FE3E-B672-4F1A-B2C0-9BA3A472D26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4E5D26-CAE1-424E-AA69-A7E656C611F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12510" yWindow="0" windowWidth="12780" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="18900" windowHeight="11770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>姓名</t>
   </si>
@@ -227,6 +227,14 @@
   </si>
   <si>
     <t>孙祥延</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李子熙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024 ICPC昆明 金牌#17</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -279,7 +287,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -288,6 +296,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -555,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="24.36328125" bestFit="1" customWidth="1"/>
@@ -616,7 +625,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E40" si="0">SUM(B3:D3)</f>
+        <f t="shared" ref="E3:E41" si="0">SUM(B3:D3)</f>
         <v>0</v>
       </c>
     </row>
@@ -1332,6 +1341,27 @@
       <c r="E40">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
